--- a/artfynd/A 39648-2026 artfynd.xlsx
+++ b/artfynd/A 39648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193865</v>
       </c>
       <c r="B2" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
